--- a/Assets/Excels/Item.xlsx
+++ b/Assets/Excels/Item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11400" windowHeight="4650"/>
+    <workbookView windowWidth="16080" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>client</t>
   </si>
   <si>
     <t>物品1</t>
@@ -1029,8 +1026,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1067,105 +1064,88 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>8</v>
+      <c r="A3">
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
